--- a/fusionSectionsCDA/ig/StructureDefinition-fr-cda-plan-de-soins.xlsx
+++ b/fusionSectionsCDA/ig/StructureDefinition-fr-cda-plan-de-soins.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-16T07:52:47+00:00</t>
+    <t>2026-04-16T09:27:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fusionSectionsCDA/ig/StructureDefinition-fr-cda-plan-de-soins.xlsx
+++ b/fusionSectionsCDA/ig/StructureDefinition-fr-cda-plan-de-soins.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-16T09:27:41+00:00</t>
+    <t>2026-04-16T09:55:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fusionSectionsCDA/ig/StructureDefinition-fr-cda-plan-de-soins.xlsx
+++ b/fusionSectionsCDA/ig/StructureDefinition-fr-cda-plan-de-soins.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-16T09:55:40+00:00</t>
+    <t>2026-04-16T10:39:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fusionSectionsCDA/ig/StructureDefinition-fr-cda-plan-de-soins.xlsx
+++ b/fusionSectionsCDA/ig/StructureDefinition-fr-cda-plan-de-soins.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5329" uniqueCount="415">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5331" uniqueCount="416">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-16T10:39:58+00:00</t>
+    <t>2026-04-17T08:40:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -532,10 +532,13 @@
     <t>Section.id</t>
   </si>
   <si>
+    <t>Y</t>
+  </si>
+  <si>
+    <t>Identifiant de la section</t>
+  </si>
+  <si>
     <t>Section.code</t>
-  </si>
-  <si>
-    <t>Y</t>
   </si>
   <si>
     <t xml:space="preserve">http://hl7.org/cda/stds/core/StructureDefinition/CE
@@ -4934,7 +4937,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="33" hidden="true">
+    <row r="33">
       <c r="A33" t="s" s="2">
         <v>167</v>
       </c>
@@ -4953,7 +4956,7 @@
         <v>75</v>
       </c>
       <c r="H33" t="s" s="2">
-        <v>74</v>
+        <v>168</v>
       </c>
       <c r="I33" t="s" s="2">
         <v>74</v>
@@ -4964,8 +4967,12 @@
       <c r="K33" t="s" s="2">
         <v>95</v>
       </c>
-      <c r="L33" s="2"/>
-      <c r="M33" s="2"/>
+      <c r="L33" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="M33" t="s" s="2">
+        <v>169</v>
+      </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -5035,10 +5042,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5052,7 +5059,7 @@
         <v>75</v>
       </c>
       <c r="H34" t="s" s="2">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="I34" t="s" s="2">
         <v>74</v>
@@ -5061,13 +5068,13 @@
         <v>74</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -5118,7 +5125,7 @@
         <v>74</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
@@ -5138,10 +5145,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5237,12 +5244,12 @@
         <v>74</v>
       </c>
     </row>
-    <row r="36" hidden="true">
+    <row r="36">
       <c r="A36" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5252,13 +5259,13 @@
         <v>62</v>
       </c>
       <c r="F36" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G36" t="s" s="2">
         <v>75</v>
       </c>
       <c r="H36" t="s" s="2">
-        <v>74</v>
+        <v>168</v>
       </c>
       <c r="I36" t="s" s="2">
         <v>74</v>
@@ -5271,7 +5278,7 @@
       </c>
       <c r="L36" s="2"/>
       <c r="M36" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -5283,7 +5290,7 @@
         <v>74</v>
       </c>
       <c r="S36" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="T36" t="s" s="2">
         <v>74</v>
@@ -5322,7 +5329,7 @@
         <v>74</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
@@ -5340,28 +5347,28 @@
         <v>74</v>
       </c>
     </row>
-    <row r="37" hidden="true">
+    <row r="37">
       <c r="A37" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E37" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="F37" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G37" t="s" s="2">
         <v>75</v>
       </c>
       <c r="H37" t="s" s="2">
-        <v>74</v>
+        <v>168</v>
       </c>
       <c r="I37" t="s" s="2">
         <v>74</v>
@@ -5374,7 +5381,7 @@
       </c>
       <c r="L37" s="2"/>
       <c r="M37" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -5386,7 +5393,7 @@
         <v>74</v>
       </c>
       <c r="S37" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="T37" t="s" s="2">
         <v>74</v>
@@ -5425,7 +5432,7 @@
         <v>74</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -5445,17 +5452,17 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E38" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F38" t="s" s="2">
         <v>80</v>
@@ -5477,7 +5484,7 @@
       </c>
       <c r="L38" s="2"/>
       <c r="M38" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -5489,7 +5496,7 @@
         <v>74</v>
       </c>
       <c r="S38" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="T38" t="s" s="2">
         <v>74</v>
@@ -5528,7 +5535,7 @@
         <v>74</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -5548,17 +5555,17 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E39" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F39" t="s" s="2">
         <v>80</v>
@@ -5580,7 +5587,7 @@
       </c>
       <c r="L39" s="2"/>
       <c r="M39" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -5631,7 +5638,7 @@
         <v>74</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
@@ -5649,28 +5656,28 @@
         <v>74</v>
       </c>
     </row>
-    <row r="40" hidden="true">
+    <row r="40">
       <c r="A40" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E40" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F40" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G40" t="s" s="2">
         <v>75</v>
       </c>
       <c r="H40" t="s" s="2">
-        <v>74</v>
+        <v>168</v>
       </c>
       <c r="I40" t="s" s="2">
         <v>74</v>
@@ -5683,7 +5690,7 @@
       </c>
       <c r="L40" s="2"/>
       <c r="M40" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -5695,7 +5702,7 @@
         <v>74</v>
       </c>
       <c r="S40" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="T40" t="s" s="2">
         <v>74</v>
@@ -5734,7 +5741,7 @@
         <v>74</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
@@ -5754,10 +5761,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -5780,11 +5787,11 @@
         <v>74</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="L41" s="2"/>
       <c r="M41" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -5835,7 +5842,7 @@
         <v>74</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
@@ -5855,10 +5862,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -5885,7 +5892,7 @@
       </c>
       <c r="L42" s="2"/>
       <c r="M42" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -5936,7 +5943,7 @@
         <v>74</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -5956,17 +5963,17 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E43" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F43" t="s" s="2">
         <v>80</v>
@@ -5984,11 +5991,11 @@
         <v>74</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="L43" s="2"/>
       <c r="M43" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -6039,7 +6046,7 @@
         <v>74</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -6059,17 +6066,17 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E44" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="F44" t="s" s="2">
         <v>80</v>
@@ -6087,11 +6094,11 @@
         <v>74</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="L44" s="2"/>
       <c r="M44" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -6142,7 +6149,7 @@
         <v>74</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -6162,17 +6169,17 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E45" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F45" t="s" s="2">
         <v>80</v>
@@ -6190,11 +6197,11 @@
         <v>74</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="L45" s="2"/>
       <c r="M45" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -6245,7 +6252,7 @@
         <v>74</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -6265,10 +6272,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6282,7 +6289,7 @@
         <v>75</v>
       </c>
       <c r="H46" t="s" s="2">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="I46" t="s" s="2">
         <v>74</v>
@@ -6291,13 +6298,13 @@
         <v>74</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -6348,7 +6355,7 @@
         <v>74</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -6368,10 +6375,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -6385,7 +6392,7 @@
         <v>75</v>
       </c>
       <c r="H47" t="s" s="2">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="I47" t="s" s="2">
         <v>74</v>
@@ -6394,13 +6401,13 @@
         <v>74</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -6451,7 +6458,7 @@
         <v>74</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -6471,10 +6478,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -6497,7 +6504,7 @@
         <v>74</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L48" s="2"/>
       <c r="M48" s="2"/>
@@ -6550,7 +6557,7 @@
         <v>74</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -6570,10 +6577,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -6629,25 +6636,25 @@
       </c>
       <c r="Y49" s="2"/>
       <c r="Z49" t="s" s="2">
+        <v>227</v>
+      </c>
+      <c r="AA49" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB49" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC49" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD49" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE49" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF49" t="s" s="2">
         <v>226</v>
-      </c>
-      <c r="AA49" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB49" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC49" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD49" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE49" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF49" t="s" s="2">
-        <v>225</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -6667,10 +6674,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -6693,7 +6700,7 @@
         <v>74</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="L50" s="2"/>
       <c r="M50" s="2"/>
@@ -6746,7 +6753,7 @@
         <v>74</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -6766,10 +6773,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -6792,7 +6799,7 @@
         <v>74</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="L51" s="2"/>
       <c r="M51" s="2"/>
@@ -6845,7 +6852,7 @@
         <v>74</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -6865,10 +6872,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -6891,7 +6898,7 @@
         <v>74</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="L52" s="2"/>
       <c r="M52" s="2"/>
@@ -6944,7 +6951,7 @@
         <v>74</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -6964,10 +6971,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -6981,7 +6988,7 @@
         <v>81</v>
       </c>
       <c r="H53" t="s" s="2">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="I53" t="s" s="2">
         <v>74</v>
@@ -6990,7 +6997,7 @@
         <v>74</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L53" s="2"/>
       <c r="M53" s="2"/>
@@ -7031,7 +7038,7 @@
         <v>74</v>
       </c>
       <c r="AB53" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="AC53" s="2"/>
       <c r="AD53" t="s" s="2">
@@ -7041,7 +7048,7 @@
         <v>124</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -7061,13 +7068,13 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C54" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="D54" t="s" s="2">
         <v>74</v>
@@ -7089,7 +7096,7 @@
         <v>74</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L54" s="2"/>
       <c r="M54" s="2"/>
@@ -7142,7 +7149,7 @@
         <v>74</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
@@ -7162,10 +7169,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -7263,10 +7270,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -7364,10 +7371,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -7465,10 +7472,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -7566,10 +7573,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -7669,10 +7676,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -7772,10 +7779,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -7875,10 +7882,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -7978,10 +7985,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -8079,10 +8086,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -8112,7 +8119,7 @@
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q64" s="2"/>
       <c r="R64" t="s" s="2">
@@ -8138,7 +8145,7 @@
       </c>
       <c r="Y64" s="2"/>
       <c r="Z64" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>74</v>
@@ -8156,7 +8163,7 @@
         <v>74</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
@@ -8176,10 +8183,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -8213,7 +8220,7 @@
       </c>
       <c r="Q65" s="2"/>
       <c r="R65" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="S65" t="s" s="2">
         <v>74</v>
@@ -8255,7 +8262,7 @@
         <v>74</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
@@ -8275,10 +8282,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -8301,7 +8308,7 @@
         <v>74</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="L66" s="2"/>
       <c r="M66" s="2"/>
@@ -8354,7 +8361,7 @@
         <v>74</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>80</v>
@@ -8374,10 +8381,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -8400,7 +8407,7 @@
         <v>74</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="L67" s="2"/>
       <c r="M67" s="2"/>
@@ -8453,7 +8460,7 @@
         <v>74</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>80</v>
@@ -8473,10 +8480,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -8499,7 +8506,7 @@
         <v>74</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="L68" s="2"/>
       <c r="M68" s="2"/>
@@ -8552,7 +8559,7 @@
         <v>74</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>80</v>
@@ -8572,10 +8579,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -8598,7 +8605,7 @@
         <v>74</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="L69" s="2"/>
       <c r="M69" s="2"/>
@@ -8651,7 +8658,7 @@
         <v>74</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>80</v>
@@ -8671,10 +8678,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -8697,7 +8704,7 @@
         <v>74</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="L70" s="2"/>
       <c r="M70" s="2"/>
@@ -8750,7 +8757,7 @@
         <v>74</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>80</v>
@@ -8770,10 +8777,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -8796,10 +8803,10 @@
         <v>74</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="M71" s="2"/>
       <c r="N71" s="2"/>
@@ -8851,7 +8858,7 @@
         <v>74</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>80</v>
@@ -8871,10 +8878,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -8897,7 +8904,7 @@
         <v>74</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="L72" s="2"/>
       <c r="M72" s="2"/>
@@ -8950,7 +8957,7 @@
         <v>74</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>80</v>
@@ -8970,10 +8977,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -8996,7 +9003,7 @@
         <v>74</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="L73" s="2"/>
       <c r="M73" s="2"/>
@@ -9049,7 +9056,7 @@
         <v>74</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>80</v>
@@ -9069,10 +9076,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -9095,7 +9102,7 @@
         <v>74</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="L74" s="2"/>
       <c r="M74" s="2"/>
@@ -9148,7 +9155,7 @@
         <v>74</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>80</v>
@@ -9168,13 +9175,13 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C75" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D75" t="s" s="2">
         <v>74</v>
@@ -9196,7 +9203,7 @@
         <v>74</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L75" s="2"/>
       <c r="M75" s="2"/>
@@ -9249,7 +9256,7 @@
         <v>74</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>80</v>
@@ -9269,10 +9276,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -9370,10 +9377,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -9471,10 +9478,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -9572,10 +9579,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -9673,10 +9680,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -9776,10 +9783,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -9879,10 +9886,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -9982,10 +9989,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -10085,10 +10092,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -10186,10 +10193,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -10219,7 +10226,7 @@
       <c r="N85" s="2"/>
       <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q85" s="2"/>
       <c r="R85" t="s" s="2">
@@ -10245,7 +10252,7 @@
       </c>
       <c r="Y85" s="2"/>
       <c r="Z85" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="AA85" t="s" s="2">
         <v>74</v>
@@ -10263,7 +10270,7 @@
         <v>74</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>80</v>
@@ -10283,10 +10290,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -10320,7 +10327,7 @@
       </c>
       <c r="Q86" s="2"/>
       <c r="R86" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="S86" t="s" s="2">
         <v>74</v>
@@ -10362,7 +10369,7 @@
         <v>74</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>80</v>
@@ -10382,10 +10389,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -10408,7 +10415,7 @@
         <v>74</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="L87" s="2"/>
       <c r="M87" s="2"/>
@@ -10461,7 +10468,7 @@
         <v>74</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>80</v>
@@ -10481,10 +10488,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -10507,7 +10514,7 @@
         <v>74</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="L88" s="2"/>
       <c r="M88" s="2"/>
@@ -10560,7 +10567,7 @@
         <v>74</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>80</v>
@@ -10580,10 +10587,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -10606,10 +10613,10 @@
         <v>74</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="M89" s="2"/>
       <c r="N89" s="2"/>
@@ -10661,7 +10668,7 @@
         <v>74</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>80</v>
@@ -10681,10 +10688,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -10707,7 +10714,7 @@
         <v>74</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="L90" s="2"/>
       <c r="M90" s="2"/>
@@ -10760,7 +10767,7 @@
         <v>74</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>80</v>
@@ -10780,10 +10787,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -10806,7 +10813,7 @@
         <v>74</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="L91" s="2"/>
       <c r="M91" s="2"/>
@@ -10859,7 +10866,7 @@
         <v>74</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>80</v>
@@ -10879,10 +10886,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -10905,7 +10912,7 @@
         <v>74</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="L92" s="2"/>
       <c r="M92" s="2"/>
@@ -10958,7 +10965,7 @@
         <v>74</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>80</v>
@@ -10978,10 +10985,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -11004,7 +11011,7 @@
         <v>74</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="L93" s="2"/>
       <c r="M93" s="2"/>
@@ -11057,7 +11064,7 @@
         <v>74</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>80</v>
@@ -11077,10 +11084,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -11103,7 +11110,7 @@
         <v>74</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="L94" s="2"/>
       <c r="M94" s="2"/>
@@ -11156,7 +11163,7 @@
         <v>74</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>80</v>
@@ -11176,10 +11183,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -11202,7 +11209,7 @@
         <v>74</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="L95" s="2"/>
       <c r="M95" s="2"/>
@@ -11255,7 +11262,7 @@
         <v>74</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>80</v>
@@ -11275,13 +11282,13 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C96" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="D96" t="s" s="2">
         <v>74</v>
@@ -11303,7 +11310,7 @@
         <v>74</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L96" s="2"/>
       <c r="M96" s="2"/>
@@ -11356,7 +11363,7 @@
         <v>74</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>80</v>
@@ -11376,10 +11383,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -11477,10 +11484,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -11578,10 +11585,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -11679,10 +11686,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -11780,10 +11787,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -11883,10 +11890,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -11986,10 +11993,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -12089,10 +12096,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -12192,10 +12199,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -12293,10 +12300,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -12326,7 +12333,7 @@
       <c r="N106" s="2"/>
       <c r="O106" s="2"/>
       <c r="P106" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q106" s="2"/>
       <c r="R106" t="s" s="2">
@@ -12352,7 +12359,7 @@
       </c>
       <c r="Y106" s="2"/>
       <c r="Z106" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="AA106" t="s" s="2">
         <v>74</v>
@@ -12370,7 +12377,7 @@
         <v>74</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>80</v>
@@ -12390,10 +12397,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -12427,7 +12434,7 @@
       </c>
       <c r="Q107" s="2"/>
       <c r="R107" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="S107" t="s" s="2">
         <v>74</v>
@@ -12469,7 +12476,7 @@
         <v>74</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>80</v>
@@ -12489,10 +12496,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -12515,7 +12522,7 @@
         <v>74</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="L108" s="2"/>
       <c r="M108" s="2"/>
@@ -12568,7 +12575,7 @@
         <v>74</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>80</v>
@@ -12588,10 +12595,10 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -12614,7 +12621,7 @@
         <v>74</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="L109" s="2"/>
       <c r="M109" s="2"/>
@@ -12667,7 +12674,7 @@
         <v>74</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>80</v>
@@ -12687,10 +12694,10 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -12713,7 +12720,7 @@
         <v>74</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="L110" s="2"/>
       <c r="M110" s="2"/>
@@ -12766,7 +12773,7 @@
         <v>74</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>80</v>
@@ -12786,10 +12793,10 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -12812,7 +12819,7 @@
         <v>74</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="L111" s="2"/>
       <c r="M111" s="2"/>
@@ -12865,7 +12872,7 @@
         <v>74</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>80</v>
@@ -12885,10 +12892,10 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -12911,7 +12918,7 @@
         <v>74</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="L112" s="2"/>
       <c r="M112" s="2"/>
@@ -12964,7 +12971,7 @@
         <v>74</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>80</v>
@@ -12984,10 +12991,10 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -13010,7 +13017,7 @@
         <v>74</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="L113" s="2"/>
       <c r="M113" s="2"/>
@@ -13063,7 +13070,7 @@
         <v>74</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>80</v>
@@ -13083,10 +13090,10 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -13109,7 +13116,7 @@
         <v>74</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="L114" s="2"/>
       <c r="M114" s="2"/>
@@ -13162,7 +13169,7 @@
         <v>74</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>80</v>
@@ -13182,10 +13189,10 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -13208,10 +13215,10 @@
         <v>74</v>
       </c>
       <c r="K115" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="M115" s="2"/>
       <c r="N115" s="2"/>
@@ -13263,7 +13270,7 @@
         <v>74</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>80</v>
@@ -13283,10 +13290,10 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -13309,7 +13316,7 @@
         <v>74</v>
       </c>
       <c r="K116" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="L116" s="2"/>
       <c r="M116" s="2"/>
@@ -13362,7 +13369,7 @@
         <v>74</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>80</v>
@@ -13382,13 +13389,13 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C117" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="D117" t="s" s="2">
         <v>74</v>
@@ -13410,7 +13417,7 @@
         <v>74</v>
       </c>
       <c r="K117" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L117" s="2"/>
       <c r="M117" s="2"/>
@@ -13463,7 +13470,7 @@
         <v>74</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>80</v>
@@ -13483,10 +13490,10 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -13584,10 +13591,10 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -13685,10 +13692,10 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -13786,10 +13793,10 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -13887,10 +13894,10 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -13990,10 +13997,10 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -14093,10 +14100,10 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -14196,10 +14203,10 @@
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -14299,10 +14306,10 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -14400,10 +14407,10 @@
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -14433,7 +14440,7 @@
       <c r="N127" s="2"/>
       <c r="O127" s="2"/>
       <c r="P127" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q127" s="2"/>
       <c r="R127" t="s" s="2">
@@ -14459,7 +14466,7 @@
       </c>
       <c r="Y127" s="2"/>
       <c r="Z127" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="AA127" t="s" s="2">
         <v>74</v>
@@ -14477,7 +14484,7 @@
         <v>74</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>80</v>
@@ -14497,10 +14504,10 @@
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -14534,7 +14541,7 @@
       </c>
       <c r="Q128" s="2"/>
       <c r="R128" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="S128" t="s" s="2">
         <v>74</v>
@@ -14576,7 +14583,7 @@
         <v>74</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>80</v>
@@ -14596,10 +14603,10 @@
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -14622,7 +14629,7 @@
         <v>74</v>
       </c>
       <c r="K129" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="L129" s="2"/>
       <c r="M129" s="2"/>
@@ -14675,7 +14682,7 @@
         <v>74</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>80</v>
@@ -14695,10 +14702,10 @@
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -14721,7 +14728,7 @@
         <v>74</v>
       </c>
       <c r="K130" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="L130" s="2"/>
       <c r="M130" s="2"/>
@@ -14774,7 +14781,7 @@
         <v>74</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>80</v>
@@ -14794,10 +14801,10 @@
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -14820,7 +14827,7 @@
         <v>74</v>
       </c>
       <c r="K131" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="L131" s="2"/>
       <c r="M131" s="2"/>
@@ -14873,7 +14880,7 @@
         <v>74</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>80</v>
@@ -14893,10 +14900,10 @@
     </row>
     <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -14919,7 +14926,7 @@
         <v>74</v>
       </c>
       <c r="K132" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="L132" s="2"/>
       <c r="M132" s="2"/>
@@ -14972,7 +14979,7 @@
         <v>74</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>80</v>
@@ -14992,10 +14999,10 @@
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -15018,7 +15025,7 @@
         <v>74</v>
       </c>
       <c r="K133" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="L133" s="2"/>
       <c r="M133" s="2"/>
@@ -15071,7 +15078,7 @@
         <v>74</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>80</v>
@@ -15091,10 +15098,10 @@
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -15117,7 +15124,7 @@
         <v>74</v>
       </c>
       <c r="K134" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="L134" s="2"/>
       <c r="M134" s="2"/>
@@ -15170,7 +15177,7 @@
         <v>74</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>80</v>
@@ -15190,10 +15197,10 @@
     </row>
     <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -15216,7 +15223,7 @@
         <v>74</v>
       </c>
       <c r="K135" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="L135" s="2"/>
       <c r="M135" s="2"/>
@@ -15269,7 +15276,7 @@
         <v>74</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>80</v>
@@ -15289,10 +15296,10 @@
     </row>
     <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -15315,10 +15322,10 @@
         <v>74</v>
       </c>
       <c r="K136" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="L136" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="M136" s="2"/>
       <c r="N136" s="2"/>
@@ -15370,7 +15377,7 @@
         <v>74</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="AG136" t="s" s="2">
         <v>80</v>
@@ -15390,10 +15397,10 @@
     </row>
     <row r="137" hidden="true">
       <c r="A137" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -15416,7 +15423,7 @@
         <v>74</v>
       </c>
       <c r="K137" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="L137" s="2"/>
       <c r="M137" s="2"/>
@@ -15469,7 +15476,7 @@
         <v>74</v>
       </c>
       <c r="AF137" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AG137" t="s" s="2">
         <v>80</v>
@@ -15489,13 +15496,13 @@
     </row>
     <row r="138" hidden="true">
       <c r="A138" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C138" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="D138" t="s" s="2">
         <v>74</v>
@@ -15517,7 +15524,7 @@
         <v>74</v>
       </c>
       <c r="K138" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L138" s="2"/>
       <c r="M138" s="2"/>
@@ -15570,7 +15577,7 @@
         <v>74</v>
       </c>
       <c r="AF138" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AG138" t="s" s="2">
         <v>80</v>
@@ -15590,10 +15597,10 @@
     </row>
     <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -15691,10 +15698,10 @@
     </row>
     <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -15792,10 +15799,10 @@
     </row>
     <row r="141" hidden="true">
       <c r="A141" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -15893,10 +15900,10 @@
     </row>
     <row r="142" hidden="true">
       <c r="A142" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -15994,10 +16001,10 @@
     </row>
     <row r="143" hidden="true">
       <c r="A143" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -16097,10 +16104,10 @@
     </row>
     <row r="144" hidden="true">
       <c r="A144" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
@@ -16200,10 +16207,10 @@
     </row>
     <row r="145" hidden="true">
       <c r="A145" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
@@ -16303,10 +16310,10 @@
     </row>
     <row r="146" hidden="true">
       <c r="A146" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
@@ -16406,10 +16413,10 @@
     </row>
     <row r="147" hidden="true">
       <c r="A147" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
@@ -16507,10 +16514,10 @@
     </row>
     <row r="148" hidden="true">
       <c r="A148" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -16540,7 +16547,7 @@
       <c r="N148" s="2"/>
       <c r="O148" s="2"/>
       <c r="P148" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q148" s="2"/>
       <c r="R148" t="s" s="2">
@@ -16566,7 +16573,7 @@
       </c>
       <c r="Y148" s="2"/>
       <c r="Z148" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="AA148" t="s" s="2">
         <v>74</v>
@@ -16584,7 +16591,7 @@
         <v>74</v>
       </c>
       <c r="AF148" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AG148" t="s" s="2">
         <v>80</v>
@@ -16604,10 +16611,10 @@
     </row>
     <row r="149" hidden="true">
       <c r="A149" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -16641,7 +16648,7 @@
       </c>
       <c r="Q149" s="2"/>
       <c r="R149" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="S149" t="s" s="2">
         <v>74</v>
@@ -16683,7 +16690,7 @@
         <v>74</v>
       </c>
       <c r="AF149" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="AG149" t="s" s="2">
         <v>80</v>
@@ -16703,10 +16710,10 @@
     </row>
     <row r="150" hidden="true">
       <c r="A150" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
@@ -16729,7 +16736,7 @@
         <v>74</v>
       </c>
       <c r="K150" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="L150" s="2"/>
       <c r="M150" s="2"/>
@@ -16782,7 +16789,7 @@
         <v>74</v>
       </c>
       <c r="AF150" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="AG150" t="s" s="2">
         <v>80</v>
@@ -16802,10 +16809,10 @@
     </row>
     <row r="151" hidden="true">
       <c r="A151" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
@@ -16828,10 +16835,10 @@
         <v>74</v>
       </c>
       <c r="K151" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="L151" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="M151" s="2"/>
       <c r="N151" s="2"/>
@@ -16883,7 +16890,7 @@
         <v>74</v>
       </c>
       <c r="AF151" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="AG151" t="s" s="2">
         <v>80</v>
@@ -16903,10 +16910,10 @@
     </row>
     <row r="152" hidden="true">
       <c r="A152" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
@@ -16929,7 +16936,7 @@
         <v>74</v>
       </c>
       <c r="K152" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="L152" s="2"/>
       <c r="M152" s="2"/>
@@ -16982,7 +16989,7 @@
         <v>74</v>
       </c>
       <c r="AF152" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="AG152" t="s" s="2">
         <v>80</v>
@@ -17002,10 +17009,10 @@
     </row>
     <row r="153" hidden="true">
       <c r="A153" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
@@ -17028,7 +17035,7 @@
         <v>74</v>
       </c>
       <c r="K153" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="L153" s="2"/>
       <c r="M153" s="2"/>
@@ -17081,7 +17088,7 @@
         <v>74</v>
       </c>
       <c r="AF153" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="AG153" t="s" s="2">
         <v>80</v>
@@ -17101,10 +17108,10 @@
     </row>
     <row r="154" hidden="true">
       <c r="A154" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
@@ -17127,7 +17134,7 @@
         <v>74</v>
       </c>
       <c r="K154" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="L154" s="2"/>
       <c r="M154" s="2"/>
@@ -17180,7 +17187,7 @@
         <v>74</v>
       </c>
       <c r="AF154" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="AG154" t="s" s="2">
         <v>80</v>
@@ -17200,10 +17207,10 @@
     </row>
     <row r="155" hidden="true">
       <c r="A155" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
@@ -17226,7 +17233,7 @@
         <v>74</v>
       </c>
       <c r="K155" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="L155" s="2"/>
       <c r="M155" s="2"/>
@@ -17279,7 +17286,7 @@
         <v>74</v>
       </c>
       <c r="AF155" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AG155" t="s" s="2">
         <v>80</v>
@@ -17299,10 +17306,10 @@
     </row>
     <row r="156" hidden="true">
       <c r="A156" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
@@ -17325,7 +17332,7 @@
         <v>74</v>
       </c>
       <c r="K156" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="L156" s="2"/>
       <c r="M156" s="2"/>
@@ -17378,7 +17385,7 @@
         <v>74</v>
       </c>
       <c r="AF156" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="AG156" t="s" s="2">
         <v>80</v>
@@ -17398,10 +17405,10 @@
     </row>
     <row r="157" hidden="true">
       <c r="A157" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
@@ -17424,7 +17431,7 @@
         <v>74</v>
       </c>
       <c r="K157" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="L157" s="2"/>
       <c r="M157" s="2"/>
@@ -17477,7 +17484,7 @@
         <v>74</v>
       </c>
       <c r="AF157" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="AG157" t="s" s="2">
         <v>80</v>
@@ -17497,10 +17504,10 @@
     </row>
     <row r="158" hidden="true">
       <c r="A158" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
@@ -17523,7 +17530,7 @@
         <v>74</v>
       </c>
       <c r="K158" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="L158" s="2"/>
       <c r="M158" s="2"/>
@@ -17576,7 +17583,7 @@
         <v>74</v>
       </c>
       <c r="AF158" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AG158" t="s" s="2">
         <v>80</v>
@@ -17596,10 +17603,10 @@
     </row>
     <row r="159" hidden="true">
       <c r="A159" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
@@ -17622,7 +17629,7 @@
         <v>74</v>
       </c>
       <c r="K159" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="L159" s="2"/>
       <c r="M159" s="2"/>
@@ -17675,7 +17682,7 @@
         <v>74</v>
       </c>
       <c r="AF159" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AG159" t="s" s="2">
         <v>80</v>
@@ -17695,10 +17702,10 @@
     </row>
     <row r="160" hidden="true">
       <c r="A160" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" t="s" s="2">
@@ -17796,10 +17803,10 @@
     </row>
     <row r="161" hidden="true">
       <c r="A161" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" t="s" s="2">
@@ -17897,10 +17904,10 @@
     </row>
     <row r="162" hidden="true">
       <c r="A162" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="C162" s="2"/>
       <c r="D162" t="s" s="2">
@@ -17998,10 +18005,10 @@
     </row>
     <row r="163" hidden="true">
       <c r="A163" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="C163" s="2"/>
       <c r="D163" t="s" s="2">
@@ -18099,10 +18106,10 @@
     </row>
     <row r="164" hidden="true">
       <c r="A164" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C164" s="2"/>
       <c r="D164" t="s" s="2">
@@ -18202,10 +18209,10 @@
     </row>
     <row r="165" hidden="true">
       <c r="A165" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="C165" s="2"/>
       <c r="D165" t="s" s="2">
@@ -18305,10 +18312,10 @@
     </row>
     <row r="166" hidden="true">
       <c r="A166" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C166" s="2"/>
       <c r="D166" t="s" s="2">
@@ -18408,10 +18415,10 @@
     </row>
     <row r="167" hidden="true">
       <c r="A167" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="C167" s="2"/>
       <c r="D167" t="s" s="2">
@@ -18511,10 +18518,10 @@
     </row>
     <row r="168" hidden="true">
       <c r="A168" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="C168" s="2"/>
       <c r="D168" t="s" s="2">
@@ -18612,10 +18619,10 @@
     </row>
     <row r="169" hidden="true">
       <c r="A169" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="C169" s="2"/>
       <c r="D169" t="s" s="2">
@@ -18642,7 +18649,7 @@
       </c>
       <c r="L169" s="2"/>
       <c r="M169" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="N169" s="2"/>
       <c r="O169" s="2"/>
@@ -18651,7 +18658,7 @@
       </c>
       <c r="Q169" s="2"/>
       <c r="R169" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="S169" t="s" s="2">
         <v>74</v>
@@ -18693,7 +18700,7 @@
         <v>74</v>
       </c>
       <c r="AF169" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="AG169" t="s" s="2">
         <v>80</v>
@@ -18713,10 +18720,10 @@
     </row>
     <row r="170" hidden="true">
       <c r="A170" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="C170" s="2"/>
       <c r="D170" t="s" s="2">
@@ -18750,7 +18757,7 @@
       </c>
       <c r="Q170" s="2"/>
       <c r="R170" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="S170" t="s" s="2">
         <v>74</v>
@@ -18792,7 +18799,7 @@
         <v>74</v>
       </c>
       <c r="AF170" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="AG170" t="s" s="2">
         <v>80</v>
@@ -18812,10 +18819,10 @@
     </row>
     <row r="171" hidden="true">
       <c r="A171" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C171" s="2"/>
       <c r="D171" t="s" s="2">
@@ -18838,7 +18845,7 @@
         <v>74</v>
       </c>
       <c r="K171" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="L171" s="2"/>
       <c r="M171" s="2"/>
@@ -18891,7 +18898,7 @@
         <v>74</v>
       </c>
       <c r="AF171" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AG171" t="s" s="2">
         <v>75</v>

--- a/fusionSectionsCDA/ig/StructureDefinition-fr-cda-plan-de-soins.xlsx
+++ b/fusionSectionsCDA/ig/StructureDefinition-fr-cda-plan-de-soins.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-17T08:40:59+00:00</t>
+    <t>2026-04-17T11:35:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fusionSectionsCDA/ig/StructureDefinition-fr-cda-plan-de-soins.xlsx
+++ b/fusionSectionsCDA/ig/StructureDefinition-fr-cda-plan-de-soins.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-17T11:35:08+00:00</t>
+    <t>2026-04-20T14:26:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
